--- a/metadados/dicionario_cbo_profissoes_saude.xlsx
+++ b/metadados/dicionario_cbo_profissoes_saude.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,67 +429,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>cbo_codigo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>descricao_original_fonte</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>titulo_oficial_cbo2002</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>grande_grupo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>familia_ocupacional</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>categoria_profissional_agregada</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>nivel_formacao</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>universo</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>incluido_universo_principal</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>justificativa</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>fonte_normativa</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>observacao_ambiguidade</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>n_registros</t>
         </is>
@@ -2848,7 +2860,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2915,7 +2927,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2982,7 +2994,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3049,7 +3061,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3116,7 +3128,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3183,7 +3195,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3246,7 +3258,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3305,7 +3317,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3368,7 +3380,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3431,7 +3443,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3494,7 +3506,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3557,7 +3569,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3620,7 +3632,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3683,7 +3695,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3746,7 +3758,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3809,7 +3821,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3872,7 +3884,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3935,7 +3947,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3998,7 +4010,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4246,7 +4258,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4305,7 +4317,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4364,7 +4376,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8532,7 +8544,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8599,7 +8611,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8666,7 +8678,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8733,7 +8745,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8800,7 +8812,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8867,7 +8879,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8930,7 +8942,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8993,7 +9005,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9056,7 +9068,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9123,7 +9135,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9190,7 +9202,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9257,7 +9269,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9324,7 +9336,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9391,7 +9403,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9454,7 +9466,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9517,7 +9529,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9580,7 +9592,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9643,7 +9655,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9710,7 +9722,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9777,7 +9789,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -18923,7 +18935,7 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
@@ -18986,7 +18998,7 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
@@ -19049,7 +19061,7 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
@@ -19112,7 +19124,7 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
@@ -19175,7 +19187,7 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
@@ -19238,7 +19250,7 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
@@ -19301,7 +19313,7 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
@@ -19364,7 +19376,7 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
@@ -19427,7 +19439,7 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
@@ -19490,7 +19502,7 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>banco de dados/sim</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
